--- a/experiment_results/combined_sweep/rtt_bursts_S1_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S1_atk5pct_wu500000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.8</t>
+          <t>00:010.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,22 +538,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.9</t>
+          <t>00:030.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.7</t>
+          <t>00:040.2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.4</t>
+          <t>00:050.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.9</t>
+          <t>00:059.8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.3</t>
+          <t>01:009.9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.1</t>
+          <t>01:020.3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.9</t>
+          <t>01:029.6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.1</t>
+          <t>01:040.6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1039,34 +1039,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.8</t>
+          <t>01:049.6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20555</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.1</t>
+          <t>02:000.4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.9</t>
+          <t>02:010.2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26375</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:019.8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25536</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.7</t>
+          <t>02:039.6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.9</t>
+          <t>02:050.2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">

--- a/experiment_results/combined_sweep/rtt_bursts_S1_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S1_atk5pct_wu500000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.5</t>
+          <t>00:010.4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.0</t>
+          <t>00:019.9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -595,22 +595,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>119</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.2</t>
+          <t>00:049.9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.8</t>
+          <t>00:059.9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>819</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.9</t>
+          <t>01:010.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.3</t>
+          <t>01:020.4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>425</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.6</t>
+          <t>01:029.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.6</t>
+          <t>01:039.9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,44 +1029,44 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.6</t>
+          <t>01:050.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.4</t>
+          <t>01:060.0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.2</t>
+          <t>02:009.9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.8</t>
+          <t>02:020.2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>678</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.3</t>
+          <t>02:029.7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.6</t>
+          <t>02:039.7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.2</t>
+          <t>02:049.8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.0</t>
+          <t>02:054.8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
